--- a/artfynd/A 51411-2024 artfynd.xlsx
+++ b/artfynd/A 51411-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133622530</v>
       </c>
       <c r="B2" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51411-2024 artfynd.xlsx
+++ b/artfynd/A 51411-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133622530</v>
       </c>
       <c r="B2" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51411-2024 artfynd.xlsx
+++ b/artfynd/A 51411-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133622530</v>
+        <v>743166</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>96231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2779</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Råstorpshage, Vg</t>
+          <t>Träd 27854 (Ask), Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>382351</v>
+        <v>382684</v>
       </c>
       <c r="R2" t="n">
-        <v>6413597</v>
+        <v>6413651</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>04:20</t>
+          <t>2008-09-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:20</t>
+          <t>2008-09-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,15 +760,848 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Lars Sjögren</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Jörgen Pettersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133622530</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Råstorpshage, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>382351</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6413597</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Fristad</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>04:20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Eskil Friberg</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Eskil Friberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133622621</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58563</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102987</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sädesärla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Motacilla alba</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hästhagen, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>382655</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6413937</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fristad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>04:20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Eskil Friberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Eskil Friberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133622604</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58519</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Råstorpshage, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>382628</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6413521</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fristad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>04:20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Eskil Friberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Eskil Friberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133622606</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58519</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Råstorpshage, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>382534</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6413456</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Fristad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>04:20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Eskil Friberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Eskil Friberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133622611</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58519</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hästhagen, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>382711</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6414000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Borgstena</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>04:20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Eskil Friberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Eskil Friberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133622542</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58107</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Råstorpshage, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>382699</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6413450</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Fristad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>04:20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Eskil Friberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Eskil Friberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>83332276</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>VGL Träd ID: 27854, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>382684</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6413651</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Fristad</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>14E389EA-0E28-46EA-AFF9-AB4B5752EEEC</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2008-09-24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2008-09-24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Inventerat av Jörgen Pettersson</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lars Sjögren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lars Sjögren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
